--- a/outputs/EH5_results_2026-05-20.xlsx
+++ b/outputs/EH5_results_2026-05-20.xlsx
@@ -647,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>80.76751479812704</v>
+        <v>86.26751479812704</v>
       </c>
       <c r="J2" t="n">
         <v>23.55539358600583</v>
@@ -671,19 +671,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>56</v>
+        <v>23.85512</v>
       </c>
       <c r="K3" t="n">
-        <v>7.544745762711865</v>
+        <v>0.06969909152542186</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.813749233609997e-14</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -781,43 +781,43 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>47.14610169491525</v>
+        <v>100.5392922033898</v>
       </c>
       <c r="AC3" t="n">
-        <v>47.14610169491525</v>
+        <v>100.5392922033898</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.86186440677966</v>
+        <v>0.1742477288135547</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -864,22 +864,22 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>31.38387755102042</v>
+        <v>14.91987755102039</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102043</v>
+        <v>67.91987755102039</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>1.254197462366058e-14</v>
+        <v>-1.667430152278574e-15</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>1.243449787580175e-14</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>1.435439870222425e-14</v>
       </c>
       <c r="M7" t="n">
         <v>16.7972</v>
@@ -1316,7 +1316,7 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.024039545778486e-14</v>
+        <v>-7.894919286223335e-14</v>
       </c>
       <c r="M8" t="n">
         <v>26.22639999999999</v>
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>85.73740000000002</v>
+        <v>85.73739999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>120.0000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>3.624848157127335e-15</v>
+        <v>-5.379274665176965e-14</v>
       </c>
       <c r="M11" t="n">
         <v>3.552713678800501e-15</v>
@@ -1744,13 +1744,13 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>253.8728452531915</v>
+        <v>253.8728452531916</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>159.7563265306122</v>
+        <v>159.7563265306123</v>
       </c>
       <c r="K12" t="n">
         <v>18.1532</v>
@@ -1759,7 +1759,7 @@
         <v>128.1165187225793</v>
       </c>
       <c r="M12" t="n">
-        <v>1.406874616804998e-14</v>
+        <v>-1.406874616804998e-14</v>
       </c>
       <c r="N12" t="n">
         <v>246.8353535353535</v>
@@ -2086,10 +2086,10 @@
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-1.392805870636948e-14</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -2196,10 +2196,10 @@
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>2.899878525701868e-14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>120</v>
@@ -2410,13 +2410,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>160.2775510204081</v>
+        <v>160.2775510204082</v>
       </c>
       <c r="K18" t="n">
         <v>16.628</v>
       </c>
       <c r="L18" t="n">
-        <v>53.72244897959186</v>
+        <v>53.72244897959183</v>
       </c>
       <c r="M18" t="n">
         <v>-1.406874616804998e-14</v>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2526,13 +2526,13 @@
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>86.17537036734696</v>
+        <v>86.17537036734693</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N19" t="n">
-        <v>261.1940656432654</v>
+        <v>261.1940656432653</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -2541,25 +2541,25 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.50000000000001</v>
+        <v>50.49999999999999</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.535000000000001</v>
+        <v>3.535</v>
       </c>
       <c r="T19" t="n">
-        <v>0.07554800000000003</v>
+        <v>0.075548</v>
       </c>
       <c r="U19" t="n">
-        <v>40.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>44.59200000000001</v>
+        <v>44.592</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>17.2364</v>
       </c>
       <c r="L20" t="n">
-        <v>80.03805036734697</v>
+        <v>80.03805036734691</v>
       </c>
       <c r="M20" t="n">
         <v>1.06581410364015e-14</v>
       </c>
       <c r="N20" t="n">
-        <v>340.4317355069389</v>
+        <v>340.4317355069388</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>412.4208906906123</v>
+        <v>412.4208906906122</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -2764,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.949729266925715e-14</v>
+        <v>9.748646334628574e-15</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -2776,10 +2776,10 @@
         <v>80.00000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.785327524179593e-14</v>
+        <v>1.392663762089796e-14</v>
       </c>
       <c r="W21" t="n">
-        <v>197.8640000000001</v>
+        <v>197.864</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2856,13 +2856,13 @@
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>53.12723404081633</v>
+        <v>53.12723404081631</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-1.685407369222958e-14</v>
       </c>
       <c r="N22" t="n">
-        <v>465.0168523910205</v>
+        <v>465.0168523910204</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -2871,22 +2871,22 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>95.50000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.949729266925715e-14</v>
+        <v>9.748646334628574e-15</v>
       </c>
       <c r="S22" t="n">
         <v>6.685</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1428680000000001</v>
+        <v>0.142868</v>
       </c>
       <c r="U22" t="n">
-        <v>76.40000000000002</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>2.785327524179593e-14</v>
+        <v>1.392663762089796e-14</v>
       </c>
       <c r="W22" t="n">
         <v>272.736</v>
@@ -2966,13 +2966,13 @@
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>96.95781934693878</v>
+        <v>96.95781934693882</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.817568318074336e-14</v>
+        <v>2.081890215777093e-14</v>
       </c>
       <c r="N23" t="n">
-        <v>561.0050935444899</v>
+        <v>561.0050935444898</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2984,7 +2984,7 @@
         <v>50.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.462296950194286e-14</v>
+        <v>-2.437161583657143e-14</v>
       </c>
       <c r="S23" t="n">
         <v>3.535</v>
@@ -2996,7 +2996,7 @@
         <v>40.40000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>2.088995643134695e-14</v>
+        <v>-3.481659405224491e-14</v>
       </c>
       <c r="W23" t="n">
         <v>312.328</v>
@@ -3070,19 +3070,19 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>77.91122448979593</v>
+        <v>128.9316326530612</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>187.0887755102039</v>
+        <v>136.0683673469387</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="N24" t="n">
-        <v>746.2229812995918</v>
+        <v>695.7127772179591</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>71.42857142857143</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>239.4417026239067</v>
+        <v>312.328</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3180,19 +3180,19 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>67.35122448979581</v>
+        <v>113.2695918367347</v>
       </c>
       <c r="K25" t="n">
         <v>13.8592</v>
       </c>
       <c r="L25" t="n">
-        <v>189.1487755102042</v>
+        <v>143.2304081632653</v>
       </c>
       <c r="M25" t="n">
-        <v>5.627498467219993e-14</v>
+        <v>-2.813749233609997e-14</v>
       </c>
       <c r="N25" t="n">
-        <v>933.4802690546938</v>
+        <v>837.5108812995918</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -3204,7 +3204,7 @@
         <v>5.5</v>
       </c>
       <c r="R25" t="n">
-        <v>50</v>
+        <v>5.000000000000027</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>71.42857142857143</v>
+        <v>7.142857142857181</v>
       </c>
       <c r="W25" t="n">
-        <v>166.5554052478134</v>
+        <v>305.0393702623907</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>115.767514798127</v>
+        <v>121.267514798127</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3507,19 +3507,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -3528,10 +3528,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -3590,16 +3590,16 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>26.70027358600583</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>23.55539358600583</v>
       </c>
       <c r="K3" t="n">
-        <v>1.26610169491525</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -3617,43 +3617,43 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.99355932203392</v>
+        <v>101.0371428571429</v>
       </c>
       <c r="AC3" t="n">
-        <v>91.99355932203392</v>
+        <v>101.0371428571429</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -3665,13 +3665,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.165254237288124</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -3700,22 +3700,22 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>57.38387755102042</v>
+        <v>40.91987755102039</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102043</v>
+        <v>67.91987755102039</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.812424078563668e-15</v>
+        <v>-1.667430152278574e-15</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>1.243449787580175e-14</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.435439870222425e-14</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>451.5319276250445</v>
+        <v>451.5319276250447</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3932,13 +3932,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>403.1092745638201</v>
+        <v>403.1092745638202</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>519.0781818181819</v>
+        <v>519.078181818182</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -4048,7 +4048,7 @@
         <v>55.0172</v>
       </c>
       <c r="N7" t="n">
-        <v>463.5052525252525</v>
+        <v>463.5052525252526</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>2.870879740444849e-14</v>
+        <v>-2.87087974044485e-14</v>
       </c>
       <c r="M8" t="n">
         <v>87.47639999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>375.1452525252525</v>
+        <v>375.1452525252526</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4268,7 +4268,7 @@
         <v>102.1764</v>
       </c>
       <c r="N9" t="n">
-        <v>271.9367676767677</v>
+        <v>271.9367676767678</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.712302604265535e-14</v>
+        <v>-7.24969631425467e-14</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4372,13 +4372,13 @@
         <v>24.5644</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.712302604265535e-14</v>
+        <v>-7.24969631425467e-14</v>
       </c>
       <c r="M10" t="n">
         <v>150.4174</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>120.0000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -4482,10 +4482,10 @@
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-5.379274665176965e-14</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N11" t="n">
         <v>120</v>
@@ -4530,16 +4530,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.894919286223336e-15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.894919286223336e-15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.406874616804998e-14</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -5020,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>360.628168033666</v>
+        <v>360.6281680336662</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5035,10 +5035,10 @@
         <v>245.9532700744824</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-4.178417611910845e-14</v>
       </c>
       <c r="N16" t="n">
-        <v>363.4937373737375</v>
+        <v>363.4937373737376</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -5089,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -5142,10 +5142,10 @@
         <v>16.628</v>
       </c>
       <c r="L17" t="n">
-        <v>600</v>
+        <v>599.9999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N17" t="n">
         <v>957.4937373737375</v>
@@ -5255,10 +5255,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>108.562</v>
+        <v>108.5620000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>847.8351515151517</v>
+        <v>847.8351515151516</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -5356,16 +5356,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>61</v>
+        <v>61.00000000000016</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>-8.612639221334548e-14</v>
       </c>
       <c r="M19" t="n">
-        <v>82.52979999999999</v>
+        <v>82.52979999999985</v>
       </c>
       <c r="N19" t="n">
         <v>764.4717171717173</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5686,13 +5686,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>13.49999999999996</v>
+        <v>13.50000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.87087974044485e-14</v>
+        <v>-8.612639221334548e-14</v>
       </c>
       <c r="M22" t="n">
         <v>124.504</v>
@@ -5906,13 +5906,13 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>7.49999999999998</v>
+        <v>7.500000000000005</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-5.741759480889699e-14</v>
       </c>
       <c r="M24" t="n">
         <v>119.003</v>
@@ -6316,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>131.7675147981271</v>
+        <v>137.2675147981271</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -6343,19 +6343,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -6364,10 +6364,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -6426,61 +6426,61 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>11.05539358600586</v>
+        <v>43.20027358600583</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>23.55539358600586</v>
+        <v>23.55539358600583</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.741007338296185e-15</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -6536,37 +6536,37 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>71.38387755102042</v>
+        <v>54.91987755102041</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102043</v>
+        <v>67.91987755102042</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.812424078563668e-15</v>
+        <v>-1.631181670707301e-14</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>-1.598721155460225e-14</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -6593,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -6649,28 +6649,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>68.42265306122449</v>
+        <v>68.42265306122448</v>
       </c>
       <c r="J5" t="n">
-        <v>85.42265306122449</v>
+        <v>85.42265306122451</v>
       </c>
       <c r="K5" t="n">
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.449939262850934e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N5" t="n">
         <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>345.0571801502971</v>
+        <v>345.057180150297</v>
       </c>
       <c r="J6" t="n">
         <v>85.42265306122449</v>
@@ -6768,13 +6768,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>281.6345270890727</v>
+        <v>281.6345270890725</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>398.8181818181819</v>
+        <v>398.8181818181818</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -6878,13 +6878,13 @@
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.741759480889699e-14</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>74.6172</v>
       </c>
       <c r="N7" t="n">
-        <v>323.4472727272728</v>
+        <v>323.4472727272727</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -6982,19 +6982,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>5.000000000000004</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>98.74639999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>223.7034343434344</v>
+        <v>223.7034343434343</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -7217,10 +7217,10 @@
         <v>120</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.214284433765954e-16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -7312,25 +7312,25 @@
         <v>158.7563265306122</v>
       </c>
       <c r="J11" t="n">
-        <v>159.7563265306122</v>
+        <v>159.7563265306123</v>
       </c>
       <c r="K11" t="n">
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>3.624848157127335e-15</v>
+        <v>-2.537393709989134e-14</v>
       </c>
       <c r="M11" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>-2.486899575160351e-14</v>
       </c>
       <c r="N11" t="n">
         <v>120</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -7642,31 +7642,31 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>162.245306122449</v>
+        <v>162.2453061224491</v>
       </c>
       <c r="K14" t="n">
         <v>22.7644</v>
       </c>
       <c r="L14" t="n">
-        <v>7.249696314254671e-15</v>
+        <v>-7.246977678136826e-14</v>
       </c>
       <c r="M14" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.102762822341903e-14</v>
       </c>
       <c r="N14" t="n">
         <v>120</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-5.362573194231713e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-6.397549157100001e-14</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -7678,10 +7678,10 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-9.139355938714288e-14</v>
       </c>
       <c r="W14" t="n">
-        <v>5</v>
+        <v>5.000000000000093</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -7746,13 +7746,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>116.2453061224489</v>
+        <v>116.245306122449</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>162.2453061224489</v>
+        <v>162.245306122449</v>
       </c>
       <c r="K15" t="n">
         <v>22.7644</v>
@@ -7767,10 +7767,10 @@
         <v>120</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -7791,7 +7791,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>5</v>
+        <v>5.000000000000093</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -7871,7 +7871,7 @@
         <v>113.9667380879506</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-2.785611741273896e-14</v>
       </c>
       <c r="N16" t="n">
         <v>232.8270707070711</v>
@@ -7880,13 +7880,13 @@
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.397549157100001e-14</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9.139355938714288e-14</v>
       </c>
       <c r="W16" t="n">
         <v>5</v>
@@ -7925,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
         <v>600</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N17" t="n">
         <v>826.8270707070711</v>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7.999999999999887</v>
+        <v>7.999999999999892</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
@@ -8742,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>46.50000000000001</v>
+        <v>46.49999999999997</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
@@ -8751,7 +8751,7 @@
         <v>-4.306319610667274e-14</v>
       </c>
       <c r="M24" t="n">
-        <v>80.783</v>
+        <v>80.78300000000003</v>
       </c>
       <c r="N24" t="n">
         <v>202.0345454545455</v>
@@ -8861,7 +8861,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>81.21420000000002</v>
+        <v>81.21419999999999</v>
       </c>
       <c r="N25" t="n">
         <v>120</v>
@@ -8876,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>9.748646334628574e-15</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -8888,10 +8888,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.392663762089796e-14</v>
       </c>
       <c r="W25" t="n">
-        <v>5</v>
+        <v>4.999999999999986</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -9152,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>132.7675147981271</v>
+        <v>138.2675147981271</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -9179,19 +9179,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -9200,10 +9200,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -9262,22 +9262,22 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.055393586005844</v>
+        <v>37.20027358600582</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>23.55539358600585</v>
+        <v>23.55539358600582</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.705036691480927e-16</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -9289,34 +9289,34 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -9372,22 +9372,22 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>61.88387755102042</v>
+        <v>45.41987755102039</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102043</v>
+        <v>67.91987755102039</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.812424078563668e-15</v>
+        <v>-1.667430152278574e-15</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>1.243449787580175e-14</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
@@ -9402,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -9429,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -9494,7 +9494,7 @@
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.435439870222425e-14</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -9592,7 +9592,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>449.0328458986901</v>
+        <v>449.0328458986902</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9604,13 +9604,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>394.1101928374655</v>
+        <v>394.1101928374657</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>510.1690909090909</v>
+        <v>510.169090909091</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -9720,7 +9720,7 @@
         <v>70.2072</v>
       </c>
       <c r="N7" t="n">
-        <v>439.2527272727272</v>
+        <v>439.2527272727273</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -9824,13 +9824,13 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-4.306319610667274e-14</v>
       </c>
       <c r="M8" t="n">
         <v>86.49639999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>351.8826262626262</v>
+        <v>351.8826262626263</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>140.6174</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>120.0000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -10154,7 +10154,7 @@
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>3.624848157127335e-15</v>
+        <v>-5.379274665176965e-14</v>
       </c>
       <c r="M11" t="n">
         <v>3.552713678800501e-15</v>
@@ -10252,7 +10252,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>319.8694782498246</v>
+        <v>319.8694782498245</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
         <v>161.1131517192123</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-2.813749233609997e-14</v>
       </c>
       <c r="N12" t="n">
         <v>279.5020202020202</v>
@@ -10582,13 +10582,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>156.2453061224489</v>
+        <v>156.245306122449</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>162.2453061224489</v>
+        <v>162.245306122449</v>
       </c>
       <c r="K15" t="n">
         <v>22.7644</v>
@@ -10704,10 +10704,10 @@
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>2.899878525701868e-14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>120</v>
@@ -10817,7 +10817,7 @@
         <v>600</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N17" t="n">
         <v>714</v>
@@ -10912,22 +10912,22 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>440.1664399092968</v>
+        <v>440.1664399092971</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>160.277551020408</v>
+        <v>160.2775510204083</v>
       </c>
       <c r="K18" t="n">
         <v>16.628</v>
       </c>
       <c r="L18" t="n">
-        <v>288.8888888888888</v>
+        <v>288.8888888888889</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.125499693443999e-13</v>
+        <v>-5.627498467219993e-14</v>
       </c>
       <c r="N18" t="n">
         <v>1000</v>
@@ -11022,19 +11022,19 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.782448979591777</v>
+        <v>3.782448979591854</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>8.782448979591777</v>
+        <v>8.782448979591853</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-5.741759480889699e-14</v>
       </c>
       <c r="M19" t="n">
         <v>133.703</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.500000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
         <v>17.2364</v>
@@ -11248,7 +11248,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>3.999999999999987</v>
       </c>
       <c r="K21" t="n">
         <v>17.2364</v>
@@ -11358,7 +11358,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.000000000000002</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
@@ -11578,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="M24" t="n">
         <v>116.553</v>
@@ -11991,7 +11991,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>118.267514798127</v>
+        <v>123.767514798127</v>
       </c>
       <c r="J2" t="n">
         <v>23.55539358600583</v>
@@ -12015,19 +12015,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -12101,19 +12101,19 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7.555393586005855</v>
+        <v>39.70027358600583</v>
       </c>
       <c r="J3" t="n">
-        <v>23.55539358600586</v>
+        <v>23.55539358600583</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.705036691480927e-16</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -12125,34 +12125,34 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -12208,22 +12208,22 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>73.38387755102042</v>
+        <v>56.91987755102039</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102043</v>
+        <v>67.91987755102039</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.812424078563668e-15</v>
+        <v>-1.667430152278574e-15</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>1.243449787580175e-14</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -12250,7 +12250,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -12265,7 +12265,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -12330,7 +12330,7 @@
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.435439870222425e-14</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>484.0316215338293</v>
+        <v>484.0316215338295</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12440,13 +12440,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>406.1089684726048</v>
+        <v>406.1089684726049</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>522.0478787878787</v>
+        <v>522.0478787878789</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -12550,13 +12550,13 @@
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-4.306319610667274e-14</v>
       </c>
       <c r="M7" t="n">
         <v>80.9872</v>
       </c>
       <c r="N7" t="n">
-        <v>440.2426262626262</v>
+        <v>440.2426262626263</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -12654,16 +12654,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>13.50000000000001</v>
+        <v>13.50000000000007</v>
       </c>
       <c r="K8" t="n">
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-5.741759480889699e-14</v>
       </c>
       <c r="M8" t="n">
-        <v>90.41639999999998</v>
+        <v>90.41639999999992</v>
       </c>
       <c r="N8" t="n">
         <v>348.9129292929293</v>
@@ -12776,7 +12776,7 @@
         <v>88.45639999999997</v>
       </c>
       <c r="N9" t="n">
-        <v>259.5630303030303</v>
+        <v>259.5630303030304</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -12886,7 +12886,7 @@
         <v>138.1674</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>120.0000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -12990,7 +12990,7 @@
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>3.624848157127335e-15</v>
+        <v>-5.379274665176965e-14</v>
       </c>
       <c r="M11" t="n">
         <v>3.552713678800501e-15</v>
@@ -13103,7 +13103,7 @@
         <v>158.1134578104275</v>
       </c>
       <c r="M12" t="n">
-        <v>2.813749233609997e-14</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>276.5323232323232</v>
@@ -13433,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-1.406874616804998e-14</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -13528,7 +13528,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>379.6286271704889</v>
+        <v>379.6286271704888</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -13540,13 +13540,13 @@
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>241.4537292113053</v>
+        <v>241.4537292113051</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>359.0391919191922</v>
+        <v>359.0391919191921</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -13597,7 +13597,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -13650,13 +13650,13 @@
         <v>16.628</v>
       </c>
       <c r="L17" t="n">
-        <v>600</v>
+        <v>599.9999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>953.0391919191921</v>
+        <v>953.039191919192</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -13766,7 +13766,7 @@
         <v>146.2920000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>805.2694949494951</v>
+        <v>805.269494949495</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -13817,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -13876,7 +13876,7 @@
         <v>122.2198</v>
       </c>
       <c r="N19" t="n">
-        <v>681.8151515151517</v>
+        <v>681.8151515151516</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -13986,7 +13986,7 @@
         <v>107.4414</v>
       </c>
       <c r="N20" t="n">
-        <v>573.288484848485</v>
+        <v>573.2884848484849</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -14084,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>34.50000000000001</v>
+        <v>34.50000000000008</v>
       </c>
       <c r="K21" t="n">
         <v>17.2364</v>
@@ -14093,7 +14093,7 @@
         <v>-1.435439870222425e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>101.0714</v>
+        <v>101.0713999999999</v>
       </c>
       <c r="N21" t="n">
         <v>471.1961616161618</v>
@@ -14194,16 +14194,16 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>41.49999999999991</v>
+        <v>41.49999999999997</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="M22" t="n">
-        <v>97.06400000000009</v>
+        <v>97.06400000000002</v>
       </c>
       <c r="N22" t="n">
         <v>373.1517171717173</v>
@@ -14830,16 +14830,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38.78787878787878</v>
+        <v>33.28787878787879</v>
       </c>
       <c r="K2" t="n">
-        <v>3.542198253723676</v>
+        <v>2.263215202876219</v>
       </c>
       <c r="L2" t="n">
         <v>121.2121212121212</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-5.773159728050814e-15</v>
       </c>
       <c r="N2" t="n">
         <v>120</v>
@@ -14851,19 +14851,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -14872,10 +14872,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -14884,10 +14884,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>75.7357267591166</v>
+        <v>84.87131997945558</v>
       </c>
       <c r="AC2" t="n">
-        <v>75.7357267591166</v>
+        <v>84.87131997945558</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -14899,7 +14899,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>8.85549563430919</v>
+        <v>5.658038007190548</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -14940,19 +14940,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>84.38387755102043</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="K3" t="n">
         <v>14.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>69.61612244897958</v>
+        <v>37.47124244897959</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>7.034373084024992e-15</v>
       </c>
       <c r="N3" t="n">
-        <v>188.9199612244898</v>
+        <v>157.0965300244898</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -14961,34 +14961,34 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -15056,13 +15056,13 @@
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>53.6161224489796</v>
+        <v>53.61612244897963</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.364242052659394e-15</v>
       </c>
       <c r="N4" t="n">
-        <v>241.9999224489796</v>
+        <v>210.1764912489796</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -15074,7 +15074,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-1.462296950194286e-14</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -15086,10 +15086,10 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.088995643134695e-14</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>28.52000000000002</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -15101,7 +15101,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-5.871749335264574e-16</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -15160,19 +15160,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>85.42265306122449</v>
+        <v>68.9586530612245</v>
       </c>
       <c r="K5" t="n">
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>42.07734693877551</v>
+        <v>58.54134693877553</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="N5" t="n">
-        <v>283.6564959183673</v>
+        <v>268.1324247183674</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -15184,7 +15184,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>16.13472000000001</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -15196,10 +15196,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>5.000000000000011</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -15211,7 +15211,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -15276,13 +15276,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>35.57734693877551</v>
+        <v>35.57734693877556</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>318.8780693877551</v>
+        <v>303.3539981877552</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>5.000000000000011</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -15386,13 +15386,13 @@
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>16.86000000000005</v>
+        <v>16.85999999999998</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-7.31148475097143e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>335.5694693877551</v>
+        <v>320.0453981877552</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -15404,7 +15404,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>7.31148475097143e-15</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -15416,7 +15416,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.044497821567347e-14</v>
       </c>
       <c r="W7" t="n">
         <v>5</v>
@@ -15490,19 +15490,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>95.50000000000003</v>
+        <v>95.5</v>
       </c>
       <c r="K8" t="n">
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>4.306319610667274e-14</v>
       </c>
       <c r="M8" t="n">
-        <v>10.05639999999996</v>
+        <v>10.05639999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>325.4114895897754</v>
+        <v>309.8874183897755</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -15609,10 +15609,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>22.79640000000003</v>
+        <v>22.79639999999997</v>
       </c>
       <c r="N9" t="n">
-        <v>302.3848229231087</v>
+        <v>286.8607517231088</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -15722,7 +15722,7 @@
         <v>74.95740000000002</v>
       </c>
       <c r="N10" t="n">
-        <v>226.6702774685632</v>
+        <v>211.1462062685633</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -15814,28 +15814,28 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.497576842982074</v>
+        <v>17.18005693277788</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>51.99757684298205</v>
+        <v>67.68005693277787</v>
       </c>
       <c r="K11" t="n">
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="M11" t="n">
-        <v>105.6035746938776</v>
+        <v>90.23474420587767</v>
       </c>
       <c r="N11" t="n">
         <v>120</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.736951571734002e-17</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -15871,7 +15871,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -15924,31 +15924,31 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>225.375957180546</v>
+        <v>225.3759571805459</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>159.7563265306123</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="K12" t="n">
         <v>18.1532</v>
       </c>
       <c r="L12" t="n">
-        <v>97.61963064993373</v>
+        <v>97.6196306499337</v>
       </c>
       <c r="M12" t="n">
         <v>2.813749233609997e-14</v>
       </c>
       <c r="N12" t="n">
-        <v>216.6434343434344</v>
+        <v>216.6434343434343</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -16144,31 +16144,31 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>83.74530612244892</v>
+        <v>83.74530612244895</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>162.245306122449</v>
+        <v>162.2453061224491</v>
       </c>
       <c r="K14" t="n">
         <v>22.7644</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.145910109019382e-14</v>
+        <v>-7.974665945680138e-14</v>
       </c>
       <c r="M14" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.815970093361102e-14</v>
       </c>
       <c r="N14" t="n">
         <v>120</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-3.575048796154476e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -16213,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -16254,31 +16254,31 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>89.74530612244895</v>
+        <v>89.74530612244899</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>162.2453061224489</v>
+        <v>162.245306122449</v>
       </c>
       <c r="K15" t="n">
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M15" t="n">
-        <v>1.392805870636948e-14</v>
+        <v>2.785611741273897e-14</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -16364,13 +16364,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>81.67489795918368</v>
+        <v>81.67489795918362</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>147.1748979591837</v>
+        <v>147.1748979591836</v>
       </c>
       <c r="K16" t="n">
         <v>21.4324</v>
@@ -16385,16 +16385,16 @@
         <v>120</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.419646622480286e-13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -16406,10 +16406,10 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.028066603543266e-13</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>4.999999999999793</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -16421,7 +16421,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.185801506327197e-15</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -16433,7 +16433,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -16474,13 +16474,13 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>578.7673479799021</v>
+        <v>578.7673479799022</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204083</v>
       </c>
       <c r="K17" t="n">
         <v>16.628</v>
@@ -16489,7 +16489,7 @@
         <v>487.9897969594939</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.417532757841401e-14</v>
       </c>
       <c r="N17" t="n">
         <v>603.109898989899</v>
@@ -16504,7 +16504,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-8.530065542800002e-14</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -16516,10 +16516,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.218580791828572e-13</v>
       </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>4.999999999999917</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -16543,7 +16543,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -16599,10 +16599,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>86.51199999999992</v>
+        <v>86.51200000000003</v>
       </c>
       <c r="N18" t="n">
-        <v>515.7240404040405</v>
+        <v>515.7240404040404</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -16614,7 +16614,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-5.666400682002858e-14</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -16626,7 +16626,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-8.094858117146941e-14</v>
       </c>
       <c r="W18" t="n">
         <v>5</v>
@@ -16653,7 +16653,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -16706,13 +16706,13 @@
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>1.291895883200182e-13</v>
       </c>
       <c r="M19" t="n">
         <v>69.29979999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>445.7242424242424</v>
+        <v>445.7242424242425</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -16810,16 +16810,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>81.50000000000006</v>
+        <v>81.5</v>
       </c>
       <c r="K20" t="n">
         <v>17.2364</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.153159805333637e-14</v>
+        <v>-3.588599675556061e-14</v>
       </c>
       <c r="M20" t="n">
-        <v>55.01139999999995</v>
+        <v>55.01139999999999</v>
       </c>
       <c r="N20" t="n">
         <v>390.1571717171718</v>
@@ -17030,16 +17030,16 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>85.50000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>2.153159805333637e-14</v>
       </c>
       <c r="M22" t="n">
-        <v>53.944</v>
+        <v>53.94400000000001</v>
       </c>
       <c r="N22" t="n">
         <v>286.0406060606061</v>
@@ -17140,22 +17140,22 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>79.50000000000006</v>
+        <v>79.5</v>
       </c>
       <c r="K23" t="n">
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.588599675556061e-14</v>
+        <v>-6.45947941600091e-14</v>
       </c>
       <c r="M23" t="n">
-        <v>48.44299999999996</v>
+        <v>48.44300000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>237.1082828282829</v>
+        <v>237.1082828282828</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -17250,16 +17250,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>71.50000000000003</v>
+        <v>71.50000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="M24" t="n">
-        <v>56.28299999999999</v>
+        <v>56.283</v>
       </c>
       <c r="N24" t="n">
         <v>180.2567676767677</v>
@@ -17369,7 +17369,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>59.6542</v>
+        <v>59.65419999999997</v>
       </c>
       <c r="N25" t="n">
         <v>120</v>
@@ -17384,7 +17384,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7.31148475097143e-15</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -17396,10 +17396,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.044497821567347e-14</v>
       </c>
       <c r="W25" t="n">
-        <v>5</v>
+        <v>4.999999999999989</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -17663,7 +17663,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>178.4784087213091</v>
+        <v>189.4778475540813</v>
       </c>
       <c r="J2" t="n">
         <v>84.38387755102042</v>
@@ -17672,13 +17672,13 @@
         <v>14.1452</v>
       </c>
       <c r="L2" t="n">
-        <v>135.5945311702887</v>
+        <v>141.0939700030609</v>
       </c>
       <c r="M2" t="n">
         <v>-1.77635683940025e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>134.2385858585858</v>
+        <v>139.6830303030303</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -17687,19 +17687,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -17708,10 +17708,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -17776,28 +17776,28 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>69.99999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K3" t="n">
         <v>14.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>1.713830474219903e-14</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>14.09619999999998</v>
+        <v>19.48619999999998</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -17818,10 +17818,10 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -17895,7 +17895,7 @@
         <v>14.61612244897962</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="N4" t="n">
         <v>134.4699612244898</v>
@@ -17904,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>5.5</v>
@@ -17919,7 +17919,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -18017,16 +18017,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>50.5</v>
+        <v>50.50000000000001</v>
       </c>
       <c r="R5" t="n">
         <v>4.874323167314287e-15</v>
       </c>
       <c r="S5" t="n">
-        <v>3.535</v>
+        <v>3.535000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07554800000000002</v>
+        <v>0.07554800000000003</v>
       </c>
       <c r="U5" t="n">
         <v>40.40000000000001</v>
@@ -18035,13 +18035,13 @@
         <v>6.963318810448982e-15</v>
       </c>
       <c r="W5" t="n">
-        <v>44.592</v>
+        <v>44.59200000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
@@ -18106,16 +18106,16 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>79.31865306122452</v>
+        <v>79.31865306122468</v>
       </c>
       <c r="K6" t="n">
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>75.18134693877549</v>
+        <v>75.18134693877552</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>6.217248937900877e-15</v>
       </c>
       <c r="N6" t="n">
         <v>212.3316256432653</v>
@@ -18127,25 +18127,25 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5</v>
+        <v>5.499999999999778</v>
       </c>
       <c r="R6" t="n">
-        <v>5.981919999999974</v>
+        <v>5.981919999999811</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-1.553207095901671e-14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-3.319425450669858e-16</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>-1.775093823887624e-13</v>
       </c>
       <c r="V6" t="n">
-        <v>8.545599999999963</v>
+        <v>8.54559999999973</v>
       </c>
       <c r="W6" t="n">
-        <v>35.87200000000004</v>
+        <v>35.87200000000011</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -18216,19 +18216,19 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>92.14</v>
+        <v>92.13999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>10.24945199999997</v>
+        <v>10.24945200000004</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>9.336531547887717e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>222.4785831232653</v>
+        <v>222.4785831232654</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -18237,25 +18237,25 @@
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>50.5</v>
+        <v>50.49999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.874323167314287e-15</v>
       </c>
       <c r="S7" t="n">
         <v>3.535</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07554800000000002</v>
+        <v>0.075548</v>
       </c>
       <c r="U7" t="n">
-        <v>40.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.963318810448982e-15</v>
       </c>
       <c r="W7" t="n">
-        <v>75.46400000000004</v>
+        <v>75.4640000000001</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -18323,7 +18323,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>582.3851099867693</v>
+        <v>582.3851099867692</v>
       </c>
       <c r="J8" t="n">
         <v>105.7616326530612</v>
@@ -18332,10 +18332,10 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>513.2956093337081</v>
+        <v>513.2956093337079</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.330136001342907e-14</v>
+        <v>6.195932655828073e-15</v>
       </c>
       <c r="N8" t="n">
         <v>730.6412363636363</v>
@@ -18350,7 +18350,7 @@
         <v>95.50000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.748646334628574e-15</v>
+        <v>-9.748646334628574e-15</v>
       </c>
       <c r="S8" t="n">
         <v>6.685</v>
@@ -18362,10 +18362,10 @@
         <v>76.40000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>1.392663762089796e-14</v>
+        <v>-1.392663762089796e-14</v>
       </c>
       <c r="W8" t="n">
-        <v>150.336</v>
+        <v>150.3360000000001</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -18377,7 +18377,7 @@
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -18436,22 +18436,22 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>24.35040000000001</v>
+        <v>24.35039999999999</v>
       </c>
       <c r="K9" t="n">
         <v>19.5284</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>79.783008</v>
+        <v>79.78300799999978</v>
       </c>
       <c r="N9" t="n">
-        <v>650.0523393939393</v>
+        <v>650.0523393939395</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -18460,7 +18460,7 @@
         <v>100</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5.849187800777144e-14</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -18472,7 +18472,7 @@
         <v>80.00000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.355982572538778e-14</v>
       </c>
       <c r="W9" t="n">
         <v>228.736</v>
@@ -18552,16 +18552,16 @@
         <v>24.5644</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>116.7540079999999</v>
+        <v>116.754008</v>
       </c>
       <c r="N10" t="n">
-        <v>532.118997979798</v>
+        <v>532.1189979797981</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -18570,7 +18570,7 @@
         <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>1.949729266925715e-14</v>
+        <v>-1.949729266925715e-14</v>
       </c>
       <c r="S10" t="n">
         <v>7</v>
@@ -18579,16 +18579,16 @@
         <v>0.1496</v>
       </c>
       <c r="U10" t="n">
-        <v>80.00000000000001</v>
+        <v>80</v>
       </c>
       <c r="V10" t="n">
-        <v>2.785327524179593e-14</v>
+        <v>-2.785327524179593e-14</v>
       </c>
       <c r="W10" t="n">
-        <v>307.136</v>
+        <v>307.1360000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -18656,22 +18656,22 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>32.35040000000002</v>
+        <v>32.35040000000004</v>
       </c>
       <c r="K11" t="n">
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-1.291895883200182e-13</v>
       </c>
       <c r="M11" t="n">
-        <v>124.857808</v>
+        <v>124.8578079999999</v>
       </c>
       <c r="N11" t="n">
         <v>406.0000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -18695,7 +18695,7 @@
         <v>2.785327524179593e-14</v>
       </c>
       <c r="W11" t="n">
-        <v>385.536</v>
+        <v>385.5360000000001</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -18763,10 +18763,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>719.5841945306123</v>
+        <v>719.5841945306122</v>
       </c>
       <c r="J12" t="n">
-        <v>159.7563265306123</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="K12" t="n">
         <v>18.1532</v>
@@ -18787,31 +18787,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>95.5</v>
+        <v>95.50000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>-9.748646334628574e-15</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>6.685</v>
       </c>
       <c r="T12" t="n">
-        <v>0.142868</v>
+        <v>0.1428680000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>76.40000000000001</v>
+        <v>76.40000000000002</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.392663762089796e-14</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>460.408</v>
+        <v>460.4080000000001</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
@@ -18882,13 +18882,13 @@
         <v>19.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>75.69533703999963</v>
+        <v>75.69533703999986</v>
       </c>
       <c r="N13" t="n">
-        <v>923.54006359596</v>
+        <v>923.5400635959597</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -18897,37 +18897,37 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.5</v>
+        <v>50.49999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>2.095958961945143e-13</v>
+        <v>9.748646334628574e-15</v>
       </c>
       <c r="S13" t="n">
         <v>3.535</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07554800000000002</v>
+        <v>0.075548</v>
       </c>
       <c r="U13" t="n">
-        <v>40.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="V13" t="n">
-        <v>2.994227088493062e-13</v>
+        <v>1.392663762089796e-14</v>
       </c>
       <c r="W13" t="n">
-        <v>499.9999999999997</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>3.206520411201039e-15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.9999999999999968</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.206520411201039e-15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -18986,43 +18986,43 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>111.2248979591837</v>
+        <v>111.2248979591836</v>
       </c>
       <c r="K14" t="n">
         <v>22.7644</v>
       </c>
       <c r="L14" t="n">
-        <v>11.27510204081626</v>
+        <v>11.27510204081633</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="N14" t="n">
-        <v>934.7024146163681</v>
+        <v>934.7024146163679</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.500000000000161</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>49.99999999999993</v>
+        <v>50.00000000000008</v>
       </c>
       <c r="S14" t="n">
-        <v>1.193711796076968e-14</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.551132638473064e-16</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.364242052659393e-13</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>71.42857142857133</v>
+        <v>71.42857142857154</v>
       </c>
       <c r="W14" t="n">
         <v>427.1137026239066</v>
@@ -19031,13 +19031,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.9999999999999982</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.9999999999999982</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -19096,55 +19096,55 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>113</v>
+        <v>113.0000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>934.7024146163681</v>
+        <v>934.7024146163679</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>-2.031836605596352e-15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>5.499999999999909</v>
       </c>
       <c r="R15" t="n">
-        <v>48.2604</v>
+        <v>48.26039999999979</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-7.187286462211545e-15</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1.536025792495496e-16</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>-8.214041671098911e-14</v>
       </c>
       <c r="V15" t="n">
-        <v>68.94342857142858</v>
+        <v>68.94342857142827</v>
       </c>
       <c r="W15" t="n">
-        <v>356.7632653061224</v>
+        <v>356.7632653061226</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-1.998401444325282e-15</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
@@ -19206,58 +19206,58 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>96.15448979591797</v>
+        <v>78.38945200000009</v>
       </c>
       <c r="K16" t="n">
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>30.84551020408204</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>67.40973703999991</v>
       </c>
       <c r="N16" t="n">
-        <v>965.2394697184093</v>
+        <v>866.6117711416206</v>
       </c>
       <c r="O16" t="n">
-        <v>1.00000000000002</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>50.49999999999991</v>
       </c>
       <c r="R16" t="n">
-        <v>50.00000000000038</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.534999999999993</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.07554799999999987</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>40.39999999999993</v>
       </c>
       <c r="V16" t="n">
-        <v>71.42857142857198</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>283.8769679300285</v>
+        <v>396.3552653061225</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -19316,58 +19316,58 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>122.327558010116</v>
+        <v>64.95886605414908</v>
       </c>
       <c r="K17" t="n">
         <v>16.628</v>
       </c>
       <c r="L17" t="n">
-        <v>24.67244198988402</v>
+        <v>-7.177199351112123e-14</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>93.41231126693386</v>
       </c>
       <c r="N17" t="n">
-        <v>989.6651872883945</v>
+        <v>772.2559011750207</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>81.69991670136993</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.899458533851429e-14</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.718994169095894</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1222230753852494</v>
+      </c>
+      <c r="U17" t="n">
+        <v>65.35993336109594</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.570655048359185e-14</v>
+      </c>
+      <c r="W17" t="n">
+        <v>460.4079999999965</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>-0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>37.19099315008634</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>53.12999021440906</v>
-      </c>
-      <c r="W17" t="n">
-        <v>229.6626922010397</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -19426,7 +19426,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>116.389452</v>
+        <v>116.3894519999959</v>
       </c>
       <c r="K18" t="n">
         <v>16.628</v>
@@ -19435,10 +19435,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>43.0103370400001</v>
+        <v>43.01033704000437</v>
       </c>
       <c r="N18" t="n">
-        <v>946.2204023995055</v>
+        <v>728.8111162861273</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -19447,37 +19447,37 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.50000000000002</v>
+        <v>50.50000000000388</v>
       </c>
       <c r="R18" t="n">
-        <v>4.386890850582858e-14</v>
+        <v>-3.217053290427429e-13</v>
       </c>
       <c r="S18" t="n">
-        <v>3.535000000000001</v>
+        <v>3.535000000000271</v>
       </c>
       <c r="T18" t="n">
-        <v>0.07554800000000005</v>
+        <v>0.0755480000000058</v>
       </c>
       <c r="U18" t="n">
-        <v>40.40000000000002</v>
+        <v>40.4000000000031</v>
       </c>
       <c r="V18" t="n">
-        <v>6.266986929404084e-14</v>
+        <v>-4.595790414896327e-13</v>
       </c>
       <c r="W18" t="n">
-        <v>269.2546922010396</v>
+        <v>500</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -19536,58 +19536,58 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>125.78268</v>
+        <v>145.214081632649</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>1.076579902666818e-14</v>
+        <v>23.285918367347</v>
       </c>
       <c r="M19" t="n">
-        <v>19.04277359999998</v>
+        <v>-2.94601022687857e-12</v>
       </c>
       <c r="N19" t="n">
-        <v>926.9852775510207</v>
+        <v>751.8641754698039</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.000000000000018</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>5.500000000003872</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.462296950194286e-14</v>
+        <v>6.957023970244336e-12</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>2.710720536924782e-13</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06732000000000002</v>
+        <v>5.793197033199249e-15</v>
       </c>
       <c r="U19" t="n">
-        <v>36.00000000000001</v>
+        <v>3.097966327914037e-12</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.088995643134695e-14</v>
+        <v>9.938605671777623e-12</v>
       </c>
       <c r="W19" t="n">
-        <v>304.5346922010397</v>
+        <v>499.9999999999929</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-4.263691440725352e-16</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -19646,19 +19646,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>137.6340816326531</v>
+        <v>86.61367346938729</v>
       </c>
       <c r="K20" t="n">
         <v>17.2364</v>
       </c>
       <c r="L20" t="n">
-        <v>24.8659183673468</v>
+        <v>70.38632653060723</v>
       </c>
       <c r="M20" t="n">
-        <v>8.864731171343009e-14</v>
+        <v>8.757439218243235e-12</v>
       </c>
       <c r="N20" t="n">
-        <v>951.6025367346939</v>
+        <v>821.5466387350962</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -19667,37 +19667,37 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.500000000005009</v>
       </c>
       <c r="R20" t="n">
-        <v>-7.798917067702859e-14</v>
+        <v>49.99999999999169</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.506528400976095e-13</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>7.493952125514627e-15</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>4.007461029686966e-12</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.114131009671837e-13</v>
+        <v>71.42857142855956</v>
       </c>
       <c r="W20" t="n">
-        <v>304.5346922010398</v>
+        <v>427.1137026239156</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -19756,58 +19756,58 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>86.61367346938778</v>
+        <v>86.88945200000512</v>
       </c>
       <c r="K21" t="n">
         <v>17.2364</v>
       </c>
       <c r="L21" t="n">
-        <v>48.88632653061222</v>
+        <v>-1.436157590157536e-11</v>
       </c>
       <c r="M21" t="n">
+        <v>49.72973703999499</v>
+      </c>
+      <c r="N21" t="n">
+        <v>771.3145811189254</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>50.50000000000877</v>
+      </c>
+      <c r="R21" t="n">
+        <v>9.748646334628574e-15</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.535000000000613</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.07554800000001313</v>
+      </c>
+      <c r="U21" t="n">
+        <v>40.40000000000702</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.392663762089796e-14</v>
+      </c>
+      <c r="W21" t="n">
+        <v>466.7057026239225</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>-0</v>
       </c>
-      <c r="N21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>50.00000000000001</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>71.42857142857146</v>
-      </c>
-      <c r="W21" t="n">
-        <v>231.6483948249465</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1</v>
-      </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -19866,19 +19866,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>71.88945199999989</v>
+        <v>80.49654788102346</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>4.306319610667274e-14</v>
+        <v>9.33035915644576e-14</v>
       </c>
       <c r="M22" t="n">
-        <v>67.2823370400002</v>
+        <v>58.84738307659845</v>
       </c>
       <c r="N22" t="n">
-        <v>932.0380433939392</v>
+        <v>711.8727800314523</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -19887,37 +19887,37 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.5</v>
+        <v>42.4672160409152</v>
       </c>
       <c r="R22" t="n">
-        <v>-4.874323167314287e-15</v>
+        <v>-1.437925334357715e-12</v>
       </c>
       <c r="S22" t="n">
-        <v>3.535</v>
+        <v>2.972705122864064</v>
       </c>
       <c r="T22" t="n">
-        <v>0.07554800000000002</v>
+        <v>0.06353095519720914</v>
       </c>
       <c r="U22" t="n">
-        <v>40.40000000000001</v>
+        <v>33.97377283273216</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.963318810448982e-15</v>
+        <v>-2.054179049082449e-12</v>
       </c>
       <c r="W22" t="n">
-        <v>271.2403948249465</v>
+        <v>500.0000000000021</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0</v>
+        <v>-2.953360926095177e-14</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -19982,13 +19982,13 @@
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.659727349944679e-14</v>
+        <v>-9.644361628056916e-14</v>
       </c>
       <c r="M23" t="n">
-        <v>2.382999999999992</v>
+        <v>2.382999999998563</v>
       </c>
       <c r="N23" t="n">
-        <v>929.6309726868685</v>
+        <v>709.4657093243829</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -20000,7 +20000,7 @@
         <v>5.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.442799657525029e-12</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -20009,25 +20009,25 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.061142367892899e-12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>500</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>-0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>271.2403948249465</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -20086,58 +20086,58 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>82.88945200000042</v>
+        <v>101.2172326530604</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>30.28276734693858</v>
       </c>
       <c r="M24" t="n">
-        <v>45.1213370399996</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="N24" t="n">
-        <v>884.0538645656568</v>
+        <v>739.4456489978521</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50.49999999999993</v>
+        <v>5.500000000001052</v>
       </c>
       <c r="R24" t="n">
-        <v>1.462296950194286e-14</v>
+        <v>27.16011200000075</v>
       </c>
       <c r="S24" t="n">
-        <v>3.534999999999995</v>
+        <v>7.361222742474638e-14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.07554799999999991</v>
+        <v>1.573198460391723e-15</v>
       </c>
       <c r="U24" t="n">
-        <v>40.39999999999995</v>
+        <v>8.412825991399588e-13</v>
       </c>
       <c r="V24" t="n">
-        <v>2.088995643134695e-14</v>
+        <v>38.80016000000107</v>
       </c>
       <c r="W24" t="n">
-        <v>310.8323948249464</v>
+        <v>460.4079999999997</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0</v>
+        <v>1.000000000000028</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -20196,58 +20196,58 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>67.351224489796</v>
+        <v>84.88945200000038</v>
       </c>
       <c r="K25" t="n">
         <v>13.8592</v>
       </c>
       <c r="L25" t="n">
-        <v>66.148775510204</v>
+        <v>3.268784468135802e-14</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.813749233609997e-14</v>
+        <v>32.81253703999965</v>
       </c>
       <c r="N25" t="n">
-        <v>949.5411523207588</v>
+        <v>706.3016721897717</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.5</v>
+        <v>50.50000000000035</v>
       </c>
       <c r="R25" t="n">
-        <v>50</v>
+        <v>4.386890850582858e-14</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.535000000000025</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.07554800000000053</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>40.40000000000028</v>
       </c>
       <c r="V25" t="n">
-        <v>71.42857142857143</v>
+        <v>6.266986929404084e-14</v>
       </c>
       <c r="W25" t="n">
-        <v>237.9460974488531</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>186.0959987631416</v>
+        <v>191.5959987631416</v>
       </c>
       <c r="J2" t="n">
         <v>84.38387755102042</v>
@@ -20523,19 +20523,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -20544,10 +20544,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -20609,31 +20609,31 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>71.38387755102043</v>
+        <v>76.8838775510204</v>
       </c>
       <c r="J3" t="n">
-        <v>84.38387755102043</v>
+        <v>84.38387755102046</v>
       </c>
       <c r="K3" t="n">
         <v>14.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-4.349817788552802e-14</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.406874616804998e-14</v>
+        <v>-4.263256414560601e-14</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-9.473903143468003e-17</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-6.873764315749458e-16</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -20719,10 +20719,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>72.88387755102042</v>
+        <v>78.3838775510204</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102045</v>
+        <v>84.38387755102043</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
@@ -20737,13 +20737,13 @@
         <v>120</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -20764,10 +20764,10 @@
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -20829,7 +20829,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>74.92265306122449</v>
+        <v>80.42265306122448</v>
       </c>
       <c r="J5" t="n">
         <v>85.42265306122449</v>
@@ -20838,46 +20838,46 @@
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.380365730490802e-31</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.352896452454035e-31</v>
       </c>
       <c r="N5" t="n">
         <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.500000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.352896452454035e-31</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>7.930164461608261e-17</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.694789433509423e-18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>9.063045098980872e-16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.932709217791479e-31</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>5.000000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -20939,7 +20939,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>74.42265306122449</v>
+        <v>74.42265306122448</v>
       </c>
       <c r="J6" t="n">
         <v>85.42265306122449</v>
@@ -20948,16 +20948,16 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-6.21661458947338e-16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-6.092903959142859e-16</v>
       </c>
       <c r="N6" t="n">
         <v>120</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
         <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>-7.31148475097143e-15</v>
+        <v>6.092903959142859e-16</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -20975,16 +20975,16 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.044497821567347e-14</v>
+        <v>8.704148513061227e-16</v>
       </c>
       <c r="W6" t="n">
-        <v>5.000000000000011</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
@@ -21049,7 +21049,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>75.14</v>
+        <v>75.13999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>92.14</v>
@@ -21067,7 +21067,7 @@
         <v>120</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -21076,7 +21076,7 @@
         <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>7.31148475097143e-15</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -21088,7 +21088,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.044497821567347e-14</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>5</v>
@@ -21159,7 +21159,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>87.76163265306121</v>
+        <v>87.76163265306123</v>
       </c>
       <c r="J8" t="n">
         <v>105.7616326530612</v>
@@ -21168,37 +21168,37 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.451872515201403e-15</v>
+        <v>-3.624848157127335e-15</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.422980252148895e-15</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="N8" t="n">
         <v>120</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.499999999999976</v>
+        <v>5.5</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.634058814185361e-14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.12679458322751e-15</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.545263852154795e-17</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.430622380831441e-14</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.334369734550516e-14</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>5</v>
@@ -21207,13 +21207,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.110223024625157e-15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.268117628370721e-16</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -21290,28 +21290,28 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.49999999999999</v>
+        <v>50.50000000000001</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.534999999999999</v>
+        <v>3.535000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.075548</v>
+        <v>0.07554800000000003</v>
       </c>
       <c r="U9" t="n">
-        <v>40.4</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>44.592</v>
+        <v>44.59200000000001</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -21323,7 +21323,7 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -21406,7 +21406,7 @@
         <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.160112</v>
+        <v>27.16011200000001</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -21415,16 +21415,16 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>38.80016</v>
+        <v>38.80016000000001</v>
       </c>
       <c r="W10" t="n">
         <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
@@ -21492,13 +21492,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.000000000000031</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-8.612639221334548e-14</v>
       </c>
       <c r="M11" t="n">
         <v>154.6012</v>
@@ -21507,43 +21507,43 @@
         <v>120</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.626066835748703e-17</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.499999999999972</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.827821147840851e-14</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.378984209497151e-15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.084229110582484e-17</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.718839096568173e-14</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.611173068344074e-14</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>5</v>
       </c>
       <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>-0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.000000000000001</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1.110223024625157e-15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-4.012621213366688e-16</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -21623,25 +21623,25 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.49999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="R12" t="n">
         <v>4.874323167314287e-15</v>
       </c>
       <c r="S12" t="n">
-        <v>3.534999999999999</v>
+        <v>3.535</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07554799999999999</v>
+        <v>0.07554800000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>40.39999999999999</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>6.963318810448982e-15</v>
       </c>
       <c r="W12" t="n">
-        <v>44.59199999999998</v>
+        <v>44.592</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -21709,7 +21709,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.499999999999977</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -21733,25 +21733,25 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.499999999999979</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.88473829136152e-15</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.657933050106901e-15</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.543239775657034e-17</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.894780628693601e-14</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6924832733736e-15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>44.59199999999996</v>
+        <v>44.592</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -21760,7 +21760,7 @@
         <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -21819,10 +21819,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>813.8558541224487</v>
+        <v>813.855854122449</v>
       </c>
       <c r="J14" t="n">
-        <v>162.2453061224489</v>
+        <v>162.245306122449</v>
       </c>
       <c r="K14" t="n">
         <v>22.7644</v>
@@ -21831,7 +21831,7 @@
         <v>600</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.231104190286715e-15</v>
       </c>
       <c r="N14" t="n">
         <v>1000</v>
@@ -21843,25 +21843,25 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.49999999999999</v>
+        <v>50.49999999999995</v>
       </c>
       <c r="R14" t="n">
-        <v>3.899458533851429e-14</v>
+        <v>4.874323167314287e-15</v>
       </c>
       <c r="S14" t="n">
-        <v>3.534999999999999</v>
+        <v>3.534999999999996</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07554799999999999</v>
+        <v>0.07554799999999993</v>
       </c>
       <c r="U14" t="n">
-        <v>40.39999999999999</v>
+        <v>40.39999999999996</v>
       </c>
       <c r="V14" t="n">
-        <v>5.570655048359185e-14</v>
+        <v>6.963318810448982e-15</v>
       </c>
       <c r="W14" t="n">
-        <v>84.1839999999999</v>
+        <v>84.18399999999995</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -21929,46 +21929,46 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>185.0402516734698</v>
+        <v>185.0402516734695</v>
       </c>
       <c r="J15" t="n">
-        <v>84.71238367346976</v>
+        <v>84.7123836734697</v>
       </c>
       <c r="K15" t="n">
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1.957418004848761e-13</v>
       </c>
       <c r="M15" t="n">
-        <v>75.98226399999959</v>
+        <v>75.98226399999963</v>
       </c>
       <c r="N15" t="n">
-        <v>923.2502383838388</v>
+        <v>923.2502383838386</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>95.5000000000001</v>
+        <v>95.50000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.924593900388572e-14</v>
+        <v>-9.748646334628574e-15</v>
       </c>
       <c r="S15" t="n">
-        <v>6.685000000000006</v>
+        <v>6.685</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1428680000000002</v>
+        <v>0.1428680000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>76.40000000000008</v>
+        <v>76.40000000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.177991286269389e-14</v>
+        <v>-1.392663762089796e-14</v>
       </c>
       <c r="W15" t="n">
         <v>159.056</v>
@@ -22039,22 +22039,22 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>51.61054799999988</v>
+        <v>51.61054799999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.612639221334548e-14</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="M16" t="n">
         <v>144.2314</v>
       </c>
       <c r="N16" t="n">
-        <v>777.5619555555559</v>
+        <v>777.5619555555558</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -22063,22 +22063,22 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.49999999999996</v>
+        <v>50.49999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>4.874323167314287e-15</v>
+        <v>9.748646334628574e-15</v>
       </c>
       <c r="S16" t="n">
-        <v>3.534999999999996</v>
+        <v>3.535</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07554799999999993</v>
+        <v>0.075548</v>
       </c>
       <c r="U16" t="n">
-        <v>40.39999999999996</v>
+        <v>40.4</v>
       </c>
       <c r="V16" t="n">
-        <v>6.963318810448982e-15</v>
+        <v>1.392663762089796e-14</v>
       </c>
       <c r="W16" t="n">
         <v>198.648</v>
@@ -22087,10 +22087,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.865174681370263e-15</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.9999999999999981</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -22149,22 +22149,22 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5000000000000284</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
         <v>16.628</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="M17" t="n">
         <v>156.582</v>
       </c>
       <c r="N17" t="n">
-        <v>619.3983191919195</v>
+        <v>619.3983191919194</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -22274,7 +22274,7 @@
         <v>150.212</v>
       </c>
       <c r="N18" t="n">
-        <v>467.6690262626266</v>
+        <v>467.6690262626265</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -22369,16 +22369,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>37.11054799999997</v>
+        <v>37.11054799999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.900174431673878e-14</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.87087974044485e-14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>142.3098</v>
@@ -22393,22 +22393,22 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.5</v>
+        <v>50.49999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>-4.874323167314287e-15</v>
+        <v>9.748646334628574e-15</v>
       </c>
       <c r="S19" t="n">
         <v>3.535</v>
       </c>
       <c r="T19" t="n">
-        <v>0.07554800000000002</v>
+        <v>0.075548</v>
       </c>
       <c r="U19" t="n">
-        <v>40.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.963318810448982e-15</v>
+        <v>1.392663762089796e-14</v>
       </c>
       <c r="W19" t="n">
         <v>238.24</v>
@@ -22479,7 +22479,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>821.4619496326532</v>
+        <v>821.461949632653</v>
       </c>
       <c r="J20" t="n">
         <v>137.6340816326531</v>
@@ -22491,10 +22491,10 @@
         <v>600</v>
       </c>
       <c r="M20" t="n">
-        <v>-8.839151632855645e-15</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="N20" t="n">
-        <v>917.9217535353539</v>
+        <v>917.9217535353538</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -22506,7 +22506,7 @@
         <v>95.50000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>1.949729266925715e-14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>6.685</v>
@@ -22518,7 +22518,7 @@
         <v>76.40000000000002</v>
       </c>
       <c r="V20" t="n">
-        <v>2.785327524179593e-14</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>313.112</v>
@@ -22589,13 +22589,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>36.6105479999999</v>
+        <v>36.61054800000001</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>17.23639999999999</v>
+        <v>17.2364</v>
       </c>
       <c r="L21" t="n">
         <v>-8.612639221334548e-14</v>
@@ -22604,7 +22604,7 @@
         <v>134.8814</v>
       </c>
       <c r="N21" t="n">
-        <v>781.6779151515154</v>
+        <v>781.6779151515153</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -22613,22 +22613,22 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.50000000000002</v>
+        <v>50.50000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.462296950194286e-14</v>
+        <v>-1.949729266925715e-14</v>
       </c>
       <c r="S21" t="n">
         <v>3.535000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.07554800000000005</v>
+        <v>0.07554800000000003</v>
       </c>
       <c r="U21" t="n">
-        <v>40.40000000000002</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.088995643134695e-14</v>
+        <v>-2.785327524179593e-14</v>
       </c>
       <c r="W21" t="n">
         <v>352.704</v>
@@ -22661,7 +22661,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>43.09099999999997</v>
+        <v>43.091</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -22708,7 +22708,7 @@
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>7.177199351112123e-14</v>
       </c>
       <c r="M22" t="n">
         <v>119.215136</v>
@@ -22753,7 +22753,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0.9999999999999843</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -22812,16 +22812,16 @@
         <v>16.64487999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.136984384193427e-13</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>4.306319610667274e-14</v>
+        <v>-4.306319610667274e-14</v>
       </c>
       <c r="M23" t="n">
-        <v>126.3530000000001</v>
+        <v>126.353</v>
       </c>
       <c r="N23" t="n">
         <v>533.6292929292931</v>
@@ -22830,25 +22830,25 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>30</v>
       </c>
       <c r="R23" t="n">
-        <v>1.462296950194286e-14</v>
+        <v>-2.193445425291429e-14</v>
       </c>
       <c r="S23" t="n">
         <v>2.1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.04488000000000001</v>
+        <v>0.04488000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>24</v>
+        <v>24.00000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>2.088995643134695e-14</v>
+        <v>-3.133493464702042e-14</v>
       </c>
       <c r="W23" t="n">
         <v>362.8</v>
@@ -22857,7 +22857,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
@@ -22919,10 +22919,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>63.36219999999991</v>
+        <v>63.3622</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.625218039592348e-15</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
@@ -22943,22 +22943,22 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>75.00000000000003</v>
+        <v>75.00000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>1.462296950194286e-14</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.250000000000002</v>
+        <v>5.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1122000000000001</v>
+        <v>0.1122</v>
       </c>
       <c r="U24" t="n">
-        <v>60.00000000000004</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>2.088995643134695e-14</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>421.6</v>
@@ -23029,13 +23029,13 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>825.521232653061</v>
+        <v>825.5212326530612</v>
       </c>
       <c r="J25" t="n">
-        <v>118.371632653061</v>
+        <v>118.3716326530612</v>
       </c>
       <c r="K25" t="n">
-        <v>13.85919999999974</v>
+        <v>13.85919999999998</v>
       </c>
       <c r="L25" t="n">
         <v>600</v>
@@ -23056,7 +23056,7 @@
         <v>100</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.949729266925715e-14</v>
+        <v>1.949729266925715e-14</v>
       </c>
       <c r="S25" t="n">
         <v>7</v>
@@ -23065,10 +23065,10 @@
         <v>0.1496</v>
       </c>
       <c r="U25" t="n">
-        <v>80.00000000000001</v>
+        <v>80</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.785327524179593e-14</v>
+        <v>2.785327524179593e-14</v>
       </c>
       <c r="W25" t="n">
         <v>500</v>
@@ -23086,22 +23086,22 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.263325743325468e-13</v>
+        <v>6.315935428978669e-14</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>7.263325743325468e-13</v>
+        <v>6.315935428978669e-14</v>
       </c>
       <c r="AE25" t="n">
-        <v>6.536993168992922e-13</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>34.64799999999935</v>
+        <v>34.64799999999995</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -23335,7 +23335,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>189.0959987631416</v>
+        <v>194.5959987631416</v>
       </c>
       <c r="J2" t="n">
         <v>84.38387755102042</v>
@@ -23359,19 +23359,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -23380,10 +23380,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -23445,19 +23445,19 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>68.88387755102043</v>
+        <v>74.38387755102042</v>
       </c>
       <c r="J3" t="n">
-        <v>84.38387755102043</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="K3" t="n">
         <v>14.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.319824249890189e-14</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -23469,7 +23469,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -23490,10 +23490,10 @@
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -23555,19 +23555,19 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>66.88387755102042</v>
+        <v>99.02875755102043</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102043</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.812424078563668e-15</v>
+        <v>1.005532878787123e-14</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>-4.213518423057394e-15</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
@@ -23579,34 +23579,34 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>30.00000000000002</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.437161583657143e-15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.100000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.04488000000000003</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>24.00000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.481659405224491e-15</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>28.52000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -23621,7 +23621,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -23665,19 +23665,19 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>64.42265306122448</v>
+        <v>47.95865306122448</v>
       </c>
       <c r="J5" t="n">
-        <v>85.42265306122449</v>
+        <v>68.9586530612245</v>
       </c>
       <c r="K5" t="n">
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-3.624848157127335e-15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="N5" t="n">
         <v>120</v>
@@ -23692,7 +23692,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>16.13472000000001</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -23704,7 +23704,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W5" t="n">
         <v>5</v>
@@ -23719,7 +23719,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -23731,7 +23731,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -23775,7 +23775,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>585.775627247532</v>
+        <v>585.7756272475322</v>
       </c>
       <c r="J6" t="n">
         <v>85.42265306122449</v>
@@ -23784,13 +23784,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>526.8529741863075</v>
+        <v>526.8529741863076</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>641.5844444444444</v>
+        <v>641.5844444444446</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -23900,7 +23900,7 @@
         <v>61.8772</v>
       </c>
       <c r="N7" t="n">
-        <v>579.0822222222222</v>
+        <v>579.0822222222223</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-5.741759480889699e-14</v>
       </c>
       <c r="M8" t="n">
         <v>76.69639999999998</v>
@@ -24120,7 +24120,7 @@
         <v>81.59640000000002</v>
       </c>
       <c r="N9" t="n">
-        <v>419.190505050505</v>
+        <v>419.1905050505051</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -24227,7 +24227,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>142.0873999999999</v>
+        <v>142.0874</v>
       </c>
       <c r="N10" t="n">
         <v>275.6678787878788</v>
@@ -24328,7 +24328,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.500000000000002</v>
       </c>
       <c r="K11" t="n">
         <v>18.1532</v>
@@ -24432,13 +24432,13 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>320.3694782498246</v>
+        <v>320.3694782498245</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>159.7563265306123</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="K12" t="n">
         <v>18.1532</v>
@@ -24447,7 +24447,7 @@
         <v>161.1131517192123</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-2.813749233609997e-14</v>
       </c>
       <c r="N12" t="n">
         <v>279.5020202020202</v>
@@ -24762,13 +24762,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>159.745306122449</v>
+        <v>159.7453061224489</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>162.245306122449</v>
+        <v>162.2453061224489</v>
       </c>
       <c r="K15" t="n">
         <v>22.7644</v>
@@ -24831,7 +24831,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -24941,7 +24941,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -24997,7 +24997,7 @@
         <v>600</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N17" t="n">
         <v>981.746262626263</v>
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -25428,7 +25428,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>38.99999999999997</v>
+        <v>38.99999999999991</v>
       </c>
       <c r="K21" t="n">
         <v>17.2364</v>
@@ -25437,10 +25437,10 @@
         <v>-4.306319610667274e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>96.66140000000001</v>
+        <v>96.66140000000007</v>
       </c>
       <c r="N21" t="n">
-        <v>499.9032323232325</v>
+        <v>499.9032323232324</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -25538,7 +25538,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>41.00000000000004</v>
+        <v>41.00000000000009</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
@@ -25547,7 +25547,7 @@
         <v>-1.004807909155697e-13</v>
       </c>
       <c r="M22" t="n">
-        <v>97.55399999999997</v>
+        <v>97.55399999999992</v>
       </c>
       <c r="N22" t="n">
         <v>401.3638383838385</v>
@@ -25758,16 +25758,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>30.50000000000001</v>
+        <v>30.50000000000002</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>-5.741759480889699e-14</v>
       </c>
       <c r="M24" t="n">
-        <v>96.46299999999999</v>
+        <v>96.46299999999998</v>
       </c>
       <c r="N24" t="n">
         <v>212.9234343434343</v>
@@ -26171,7 +26171,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>122.2675147981271</v>
+        <v>151.3205050177839</v>
       </c>
       <c r="J2" t="n">
         <v>23.55539358600583</v>
@@ -26180,13 +26180,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>121.2121212121213</v>
+        <v>144.7651114317781</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>120</v>
+        <v>143.3174603174603</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -26195,19 +26195,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -26216,10 +26216,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -26243,7 +26243,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -26278,13 +26278,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05539358600581705</v>
+        <v>8.644879999999997</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>23.55539358600582</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26293,7 +26293,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.220623850414995e-14</v>
+        <v>23.0842857142857</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -26302,37 +26302,37 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -26347,13 +26347,13 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -26388,37 +26388,37 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>61.88387755102042</v>
+        <v>45.41987755102039</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102046</v>
+        <v>67.91987755102039</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.74701460214292e-14</v>
+        <v>-1.667430152278574e-15</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.672449011560276e-14</v>
+        <v>1.243449787580175e-14</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -26430,7 +26430,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -26445,7 +26445,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -26504,25 +26504,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>85.42265306122451</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="K5" t="n">
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.449939262850934e-14</v>
+        <v>1.435439870222425e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -26579,7 +26579,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -26608,7 +26608,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>395.0391207686012</v>
+        <v>395.0391207686014</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26623,16 +26623,16 @@
         <v>332.6164677073768</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>449.290303030303</v>
+        <v>449.2903030303031</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -26689,7 +26689,7 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -26724,22 +26724,22 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>26.50000000000002</v>
+        <v>26.5</v>
       </c>
       <c r="K7" t="n">
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>4.306319610667274e-14</v>
       </c>
       <c r="M7" t="n">
-        <v>64.32719999999999</v>
+        <v>64.3272</v>
       </c>
       <c r="N7" t="n">
-        <v>384.3133333333333</v>
+        <v>384.3133333333334</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -26799,7 +26799,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -26834,22 +26834,22 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>22.00000000000003</v>
+        <v>22.00000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="M8" t="n">
-        <v>82.08639999999997</v>
+        <v>82.08639999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>301.3977777777777</v>
+        <v>301.3977777777778</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -26909,7 +26909,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -26944,25 +26944,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>30.49999999999997</v>
+        <v>30.5</v>
       </c>
       <c r="K9" t="n">
         <v>19.5284</v>
       </c>
       <c r="L9" t="n">
-        <v>2.914335439641036e-14</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>73.75639999999999</v>
+        <v>73.75640000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>226.8963636363636</v>
+        <v>226.8963636363637</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -27019,7 +27019,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -27054,22 +27054,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>45.49999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="K10" t="n">
         <v>24.5644</v>
       </c>
       <c r="L10" t="n">
-        <v>1.665334536937735e-14</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>105.8274</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>120.0000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -27170,19 +27170,19 @@
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-5.379274665176965e-14</v>
       </c>
       <c r="M11" t="n">
-        <v>-0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N11" t="n">
         <v>120</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -27274,16 +27274,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>159.7563265306123</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="K12" t="n">
         <v>18.1532</v>
       </c>
       <c r="L12" t="n">
-        <v>95.11988572594635</v>
+        <v>95.1198857259464</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.813749233609997e-14</v>
       </c>
       <c r="N12" t="n">
         <v>214.1686868686869</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -27390,7 +27390,7 @@
         <v>19.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>93.227</v>
@@ -27399,7 +27399,7 @@
         <v>120</v>
       </c>
       <c r="O13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -27488,7 +27488,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>94.24530612244898</v>
+        <v>94.24530612244892</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -27500,19 +27500,19 @@
         <v>22.7644</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.801100959132841e-14</v>
+        <v>-2.145910109019382e-14</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.765259050046097e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="N14" t="n">
         <v>120</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -27598,7 +27598,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>92.24530612244897</v>
+        <v>92.24530612244902</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -27610,25 +27610,25 @@
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.785611741273897e-14</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-7.31148475097143e-15</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -27640,10 +27640,10 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.044497821567347e-14</v>
       </c>
       <c r="W15" t="n">
-        <v>5</v>
+        <v>5.000000000000011</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>117.1491352819059</v>
+        <v>76.67489795918368</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -27720,19 +27720,19 @@
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>40.47423732272213</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.803870634617627e-14</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>160.069494949495</v>
+        <v>120</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-8.006451057696044e-17</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -27753,7 +27753,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>5.000000000000011</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -27765,7 +27765,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -27789,7 +27789,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -27833,10 +27833,10 @@
         <v>600</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-2.152233946617343e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>754.0694949494949</v>
+        <v>714</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -27848,7 +27848,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>7.31148475097143e-15</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -27860,7 +27860,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.044497821567347e-14</v>
       </c>
       <c r="W17" t="n">
         <v>5</v>
@@ -27928,28 +27928,28 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>40.47836734693844</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>62.5</v>
+        <v>102.9783673469384</v>
       </c>
       <c r="K18" t="n">
         <v>16.628</v>
       </c>
       <c r="L18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>95.82200000000003</v>
+        <v>56.15320000000028</v>
       </c>
       <c r="N18" t="n">
-        <v>657.2795959595959</v>
+        <v>657.2795959595957</v>
       </c>
       <c r="O18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -28044,22 +28044,22 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>57.50000000000016</v>
+        <v>57.50000000000004</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.578983857244667e-13</v>
+        <v>7.177199351112123e-14</v>
       </c>
       <c r="M19" t="n">
-        <v>85.95979999999984</v>
+        <v>85.95979999999996</v>
       </c>
       <c r="N19" t="n">
-        <v>570.4515151515151</v>
+        <v>570.451515151515</v>
       </c>
       <c r="O19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -28154,22 +28154,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>56.00000000000006</v>
+        <v>55.99999999999992</v>
       </c>
       <c r="K20" t="n">
         <v>17.2364</v>
       </c>
       <c r="L20" t="n">
-        <v>8.612639221334548e-14</v>
+        <v>1.578983857244667e-13</v>
       </c>
       <c r="M20" t="n">
-        <v>80.00139999999995</v>
+        <v>80.00140000000007</v>
       </c>
       <c r="N20" t="n">
-        <v>489.6420202020203</v>
+        <v>489.6420202020201</v>
       </c>
       <c r="O20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -28229,7 +28229,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -28264,22 +28264,22 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>55.5</v>
+        <v>55.49999999999997</v>
       </c>
       <c r="K21" t="n">
         <v>17.2364</v>
       </c>
       <c r="L21" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>4.306319610667274e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>80.49139999999998</v>
+        <v>80.49140000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>408.3375757575758</v>
+        <v>408.3375757575757</v>
       </c>
       <c r="O21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -28315,7 +28315,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -28339,7 +28339,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
@@ -28374,25 +28374,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>56.49999999999999</v>
+        <v>56.50000000000004</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>-2.870879740444849e-14</v>
       </c>
       <c r="M22" t="n">
-        <v>82.36400000000002</v>
+        <v>82.36399999999998</v>
       </c>
       <c r="N22" t="n">
-        <v>325.1416161616162</v>
+        <v>325.1416161616161</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.11028816370329e-16</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -28484,22 +28484,22 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>61.50000000000011</v>
+        <v>61.50000000000004</v>
       </c>
       <c r="K23" t="n">
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.741759480889699e-14</v>
+        <v>7.177199351112123e-14</v>
       </c>
       <c r="M23" t="n">
-        <v>66.0829999999999</v>
+        <v>66.08299999999997</v>
       </c>
       <c r="N23" t="n">
-        <v>258.3911111111112</v>
+        <v>258.3911111111111</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.06581410364015e-16</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -28594,25 +28594,25 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>57.00000000000001</v>
+        <v>56.99999999999998</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>-8.612639221334548e-14</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>70.49299999999999</v>
+        <v>70.49300000000002</v>
       </c>
       <c r="N24" t="n">
         <v>187.1860606060606</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.291386103495536e-15</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -28645,7 +28645,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -28710,7 +28710,7 @@
         <v>13.8592</v>
       </c>
       <c r="L25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>66.51419999999997</v>
@@ -28719,7 +28719,7 @@
         <v>120</v>
       </c>
       <c r="O25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -28779,7 +28779,7 @@
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
@@ -29010,19 +29010,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>84.38387755102042</v>
+        <v>79.7878787878788</v>
       </c>
       <c r="K2" t="n">
-        <v>14.1452</v>
+        <v>13.07643554185927</v>
       </c>
       <c r="L2" t="n">
-        <v>122.1161224489796</v>
+        <v>121.2121212121212</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>-1.199040866595169e-14</v>
       </c>
       <c r="N2" t="n">
-        <v>120.8949612244898</v>
+        <v>120</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -29031,19 +29031,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -29052,10 +29052,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -29064,10 +29064,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>7.634031843862356</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7.634031843862356</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>35.363</v>
+        <v>32.69108885464817</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -29120,19 +29120,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>84.38387755102043</v>
+        <v>84.3838775510204</v>
       </c>
       <c r="K3" t="n">
         <v>14.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>138.6161224489796</v>
+        <v>90.00557444897957</v>
       </c>
       <c r="M3" t="n">
-        <v>2.813749233609997e-14</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>258.1249224489795</v>
+        <v>209.1055187044898</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -29141,34 +29141,34 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>50.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.535</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.07554800000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>44.59200000000001</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -29230,19 +29230,19 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>84.38387755102036</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="K4" t="n">
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>91.00557444897953</v>
+        <v>42.78825444897962</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.097966327914036e-15</v>
       </c>
       <c r="N4" t="n">
-        <v>348.2204411534693</v>
+        <v>251.4658906089796</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -29251,37 +29251,37 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>50.50000000000012</v>
+        <v>95.49999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>6.824052434240002e-14</v>
+        <v>-4.874323167314287e-15</v>
       </c>
       <c r="S4" t="n">
-        <v>3.535000000000008</v>
+        <v>6.684999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07554800000000018</v>
+        <v>0.142868</v>
       </c>
       <c r="U4" t="n">
-        <v>40.4000000000001</v>
+        <v>76.39999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>9.748646334628574e-14</v>
+        <v>-6.963318810448982e-15</v>
       </c>
       <c r="W4" t="n">
-        <v>44.592</v>
+        <v>119.464</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-16</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -29340,19 +29340,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>85.42265306122449</v>
+        <v>85.42265306122452</v>
       </c>
       <c r="K5" t="n">
         <v>15.2312</v>
       </c>
       <c r="L5" t="n">
-        <v>12.7494789387755</v>
+        <v>7.927746938775464</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8.242295734817138e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>360.842425302857</v>
+        <v>259.3143600783673</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -29361,37 +29361,37 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>95.50000000000007</v>
+        <v>100.0000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-2.924593900388572e-14</v>
       </c>
       <c r="S5" t="n">
-        <v>6.685000000000004</v>
+        <v>7.000000000000004</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1428680000000001</v>
+        <v>0.1496000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>76.40000000000006</v>
+        <v>80.00000000000006</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-4.177991286269389e-14</v>
       </c>
       <c r="W5" t="n">
-        <v>119.4640000000001</v>
+        <v>197.8640000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-5.684341886080802e-16</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-5.684341886080802e-16</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -29450,22 +29450,22 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>79.85040000000001</v>
+        <v>79.85040000000004</v>
       </c>
       <c r="K6" t="n">
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>4.485749594445077e-15</v>
+        <v>1.256009886444622e-14</v>
       </c>
       <c r="M6" t="n">
-        <v>5.460808</v>
+        <v>5.460807999999952</v>
       </c>
       <c r="N6" t="n">
-        <v>355.3264576260893</v>
+        <v>253.7983924015997</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -29474,7 +29474,7 @@
         <v>100</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.949729266925715e-14</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -29486,22 +29486,22 @@
         <v>80.00000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.785327524179593e-14</v>
       </c>
       <c r="W6" t="n">
-        <v>197.8640000000001</v>
+        <v>276.2640000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-9.689219124001365e-16</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-1.076579902666818e-15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.684341886080802e-16</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -29560,58 +29560,58 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>71.17213200000002</v>
+        <v>66.35040000000001</v>
       </c>
       <c r="K7" t="n">
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>3.588599675556062e-15</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="M7" t="n">
-        <v>20.54851063999998</v>
+        <v>25.27380799999998</v>
       </c>
       <c r="N7" t="n">
-        <v>334.570386272554</v>
+        <v>228.2692934117007</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>1.000000000000003</v>
       </c>
       <c r="Q7" t="n">
-        <v>95.49999999999999</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.949729266925715e-14</v>
       </c>
       <c r="S7" t="n">
-        <v>6.684999999999998</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>0.142868</v>
+        <v>0.1496</v>
       </c>
       <c r="U7" t="n">
-        <v>76.39999999999999</v>
+        <v>80</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.785327524179593e-14</v>
       </c>
       <c r="W7" t="n">
-        <v>272.736</v>
+        <v>354.664</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -29670,58 +29670,58 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>101.389452</v>
+        <v>53.17213200000003</v>
       </c>
       <c r="K8" t="n">
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.49888468366716e-14</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.284737039999964</v>
+        <v>51.53771063999996</v>
       </c>
       <c r="N8" t="n">
-        <v>330.2423690604328</v>
+        <v>176.2109998359432</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.5</v>
+        <v>95.50000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>1.462296950194286e-14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.535</v>
+        <v>6.685</v>
       </c>
       <c r="T8" t="n">
-        <v>0.07554800000000002</v>
+        <v>0.1428680000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>40.40000000000001</v>
+        <v>76.40000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>2.088995643134695e-14</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>312.328</v>
+        <v>429.5360000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -29768,10 +29768,10 @@
         <v>197.5</v>
       </c>
       <c r="F9" t="n">
-        <v>176.8094906446873</v>
+        <v>197.5</v>
       </c>
       <c r="G9" t="n">
-        <v>20.69050935531268</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -29780,19 +29780,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>54.7412244897959</v>
+        <v>105.7616326530612</v>
       </c>
       <c r="K9" t="n">
         <v>19.5284</v>
       </c>
       <c r="L9" t="n">
-        <v>116.5682661548914</v>
+        <v>37.62781934693878</v>
       </c>
       <c r="M9" t="n">
-        <v>1.406874616804998e-14</v>
+        <v>-2.813749233609997e-14</v>
       </c>
       <c r="N9" t="n">
-        <v>445.6449525537753</v>
+        <v>213.4625409894126</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -29801,37 +29801,37 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.5</v>
+        <v>50.5</v>
       </c>
       <c r="R9" t="n">
-        <v>50</v>
+        <v>1.462296950194286e-14</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.535</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.07554800000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>71.42857142857143</v>
+        <v>2.088995643134695e-14</v>
       </c>
       <c r="W9" t="n">
-        <v>239.4417026239067</v>
+        <v>469.128</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>1.13686837721616e-14</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -29890,19 +29890,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>144.1137008240568</v>
+        <v>102.4667346938775</v>
       </c>
       <c r="K10" t="n">
         <v>24.5644</v>
       </c>
       <c r="L10" t="n">
-        <v>79.38629917594322</v>
+        <v>121.0332653061225</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.627498467219993e-14</v>
+        <v>1.406874616804998e-14</v>
       </c>
       <c r="N10" t="n">
-        <v>524.2373887379591</v>
+        <v>333.2854736424738</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -29914,7 +29914,7 @@
         <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>9.185973192424385</v>
+        <v>50.00000000000004</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -29923,13 +29923,13 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>13.12281884632055</v>
+        <v>71.42857142857149</v>
       </c>
       <c r="W10" t="n">
-        <v>226.0510711480694</v>
+        <v>396.2417026239067</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -30000,19 +30000,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>108.735918367347</v>
+        <v>108.7359183673469</v>
       </c>
       <c r="K11" t="n">
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>132.264081632653</v>
+        <v>132.2640816326531</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="N11" t="n">
-        <v>655.1788295542856</v>
+        <v>464.2269144588004</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -30024,7 +30024,7 @@
         <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>49.99999999999994</v>
+        <v>50</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -30033,13 +30033,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>71.42857142857135</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="W11" t="n">
-        <v>153.1647737719762</v>
+        <v>323.3554052478134</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -30119,10 +30119,10 @@
         <v>152.2640816326531</v>
       </c>
       <c r="M12" t="n">
-        <v>2.813749233609997e-14</v>
+        <v>-2.813749233609997e-14</v>
       </c>
       <c r="N12" t="n">
-        <v>805.9202703706121</v>
+        <v>614.968355275127</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -30149,10 +30149,10 @@
         <v>71.42857142857143</v>
       </c>
       <c r="W12" t="n">
-        <v>80.27847639588293</v>
+        <v>250.4691078717201</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y12" t="n">
         <v>1</v>
@@ -30220,58 +30220,58 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>162.1295918367347</v>
+        <v>121.6716163265307</v>
       </c>
       <c r="K13" t="n">
         <v>19.8</v>
       </c>
       <c r="L13" t="n">
-        <v>77.2598601632653</v>
+        <v>166.3283836734693</v>
       </c>
       <c r="M13" t="n">
-        <v>1.406874616804998e-14</v>
+        <v>-2.813749233609997e-14</v>
       </c>
       <c r="N13" t="n">
-        <v>882.4075319322448</v>
+        <v>779.6334551118616</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9999999999999941</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.5</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>4.874323167314287e-15</v>
+        <v>39.64881600000005</v>
       </c>
       <c r="S13" t="n">
-        <v>3.535</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07554800000000002</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>40.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.963318810448982e-15</v>
+        <v>56.64116571428578</v>
       </c>
       <c r="W13" t="n">
-        <v>119.8704763958829</v>
+        <v>192.6719999999999</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -30336,13 +30336,13 @@
         <v>22.7644</v>
       </c>
       <c r="L14" t="n">
-        <v>41.42682587755104</v>
+        <v>89.64414587755111</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.172839685954386e-14</v>
       </c>
       <c r="N14" t="n">
-        <v>923.4200895510203</v>
+        <v>868.3811595306372</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -30351,25 +30351,25 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.50000000000001</v>
+        <v>50.49999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>-9.748646334628574e-15</v>
+        <v>-1.462296950194286e-14</v>
       </c>
       <c r="S14" t="n">
-        <v>6.685</v>
+        <v>3.534999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1428680000000001</v>
+        <v>0.07554799999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>76.40000000000002</v>
+        <v>40.39999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.392663762089796e-14</v>
+        <v>-2.088995643134695e-14</v>
       </c>
       <c r="W14" t="n">
-        <v>194.742476395883</v>
+        <v>232.2639999999999</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -30446,13 +30446,13 @@
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>24.10509387755104</v>
+        <v>28.92682587755103</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.275779813018744e-14</v>
+        <v>-1.055155962603749e-14</v>
       </c>
       <c r="N15" t="n">
-        <v>947.2841324897959</v>
+        <v>897.0187171494127</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -30461,31 +30461,31 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>95.49999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6.684999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1496</v>
+        <v>0.142868</v>
       </c>
       <c r="U15" t="n">
-        <v>80.00000000000001</v>
+        <v>76.39999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>273.142476395883</v>
+        <v>307.1359999999999</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
@@ -30556,13 +30556,13 @@
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>40.67550204081639</v>
+        <v>40.67550204081628</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>987.5528795102041</v>
+        <v>937.2874641698209</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -30574,7 +30574,7 @@
         <v>100</v>
       </c>
       <c r="R16" t="n">
-        <v>1.949729266925715e-14</v>
+        <v>-1.949729266925715e-14</v>
       </c>
       <c r="S16" t="n">
         <v>7</v>
@@ -30583,13 +30583,13 @@
         <v>0.1496</v>
       </c>
       <c r="U16" t="n">
-        <v>80.00000000000001</v>
+        <v>80</v>
       </c>
       <c r="V16" t="n">
-        <v>2.785327524179593e-14</v>
+        <v>-2.785327524179593e-14</v>
       </c>
       <c r="W16" t="n">
-        <v>351.5424763958829</v>
+        <v>385.5359999999999</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -30601,7 +30601,7 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -30666,13 +30666,13 @@
         <v>16.628</v>
       </c>
       <c r="L17" t="n">
-        <v>12.57284897959183</v>
+        <v>17.39458097959163</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-3.205968823749572e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>1000</v>
+        <v>954.5080993396166</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -30681,25 +30681,25 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>100</v>
+        <v>95.50000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.949729266925715e-14</v>
+        <v>-3.899458533851429e-14</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6.685</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1496</v>
+        <v>0.1428680000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>80.00000000000001</v>
+        <v>76.40000000000002</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.785327524179593e-14</v>
+        <v>-5.570655048359185e-14</v>
       </c>
       <c r="W17" t="n">
-        <v>429.942476395883</v>
+        <v>460.408</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -30770,52 +30770,52 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>160.2775510204081</v>
+        <v>160.2775510204082</v>
       </c>
       <c r="K18" t="n">
         <v>16.628</v>
       </c>
       <c r="L18" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>7.611900979591837</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.683773451892192e-14</v>
+        <v>-2.901678897160309e-14</v>
       </c>
       <c r="N18" t="n">
-        <v>1000</v>
+        <v>962.0438813094125</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.086598290914574e-11</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>57.60399383627368</v>
+        <v>50.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.462296950194286e-14</v>
+        <v>5.361755484045716e-14</v>
       </c>
       <c r="S18" t="n">
-        <v>4.032279568539157</v>
+        <v>3.535</v>
       </c>
       <c r="T18" t="n">
-        <v>0.08617557477906543</v>
+        <v>0.07554800000000002</v>
       </c>
       <c r="U18" t="n">
-        <v>46.08319506901894</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>2.088995643134695e-14</v>
+        <v>7.65965069149388e-14</v>
       </c>
       <c r="W18" t="n">
-        <v>475.1040075635215</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
@@ -30880,58 +30880,58 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>121.474545523043</v>
+        <v>140.1120408163297</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.991291613958457e-09</v>
+        <v>9.887959183670397</v>
       </c>
       <c r="M19" t="n">
-        <v>23.26474538740649</v>
+        <v>8.881784197001252e-15</v>
       </c>
       <c r="N19" t="n">
-        <v>976.5002571814766</v>
+        <v>971.8329609012462</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.086598290914573e-11</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.000000000020866</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31.75509239348953</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.140835337309909e-11</v>
+        <v>4.999999999996868</v>
       </c>
       <c r="S19" t="n">
-        <v>2.222856467544267</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.04750561822066034</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>25.40407391479162</v>
+        <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.629764767585584e-11</v>
+        <v>7.142857142852669</v>
       </c>
       <c r="W19" t="n">
-        <v>500.0000000000007</v>
+        <v>492.7113702623952</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -30990,46 +30990,46 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>105.9991481731399</v>
+        <v>99.04844535479391</v>
       </c>
       <c r="K20" t="n">
         <v>17.2364</v>
       </c>
       <c r="L20" t="n">
-        <v>21.50085182686052</v>
+        <v>28.4515546452059</v>
       </c>
       <c r="M20" t="n">
-        <v>4.515499085755437e-11</v>
+        <v>6.039613253960852e-14</v>
       </c>
       <c r="N20" t="n">
-        <v>997.7861004900229</v>
+        <v>1000</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>4.560689603749779e-11</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>5.499999999999858</v>
       </c>
       <c r="R20" t="n">
-        <v>31.00223479027773</v>
+        <v>37.81392355230191</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-9.947598300641404e-15</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-2.12594386539422e-16</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>-1.136868377216161e-13</v>
       </c>
       <c r="V20" t="n">
-        <v>44.2889068432539</v>
+        <v>54.01989078900273</v>
       </c>
       <c r="W20" t="n">
-        <v>454.8072379150477</v>
+        <v>437.5890327225964</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -31041,7 +31041,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.999999999954393</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -31100,46 +31100,46 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>84.88945200457461</v>
+        <v>85.84755628333053</v>
       </c>
       <c r="K21" t="n">
         <v>17.2364</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>6.45947941600091e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>51.68973703452601</v>
+        <v>50.75079484233606</v>
       </c>
       <c r="N21" t="n">
-        <v>945.5742448995926</v>
+        <v>948.7365708663273</v>
       </c>
       <c r="O21" t="n">
-        <v>1.127323527845341e-15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.49999999573059</v>
+        <v>49.60582560893317</v>
       </c>
       <c r="R21" t="n">
-        <v>9.908329161589789e-10</v>
+        <v>4.874323167314287e-15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.534999999701141</v>
+        <v>3.472407792625322</v>
       </c>
       <c r="T21" t="n">
-        <v>0.07554799999361297</v>
+        <v>0.07421031511096404</v>
       </c>
       <c r="U21" t="n">
-        <v>40.39999999658448</v>
+        <v>39.68466048714654</v>
       </c>
       <c r="V21" t="n">
-        <v>1.415475594512827e-09</v>
+        <v>6.963318810448982e-15</v>
       </c>
       <c r="W21" t="n">
-        <v>494.3992379102561</v>
+        <v>476.48</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -31151,7 +31151,7 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -31210,58 +31210,58 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>89.5244897959181</v>
+        <v>117.8551199999971</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>54.97551020243172</v>
+        <v>2.852936742067069e-12</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>22.23598240000284</v>
       </c>
       <c r="N22" t="n">
-        <v>1000</v>
+        <v>926.2759825834989</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="R22" t="n">
-        <v>49.99999999999996</v>
+        <v>1.218580791828572e-14</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.04488</v>
       </c>
       <c r="U22" t="n">
+        <v>24</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.740829702612245e-14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>499.9999999999999</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>-0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>71.42857142857137</v>
-      </c>
-      <c r="W22" t="n">
-        <v>421.5129405341629</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -31320,58 +31320,58 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>101.8419634656343</v>
+        <v>77.91122448979593</v>
       </c>
       <c r="K23" t="n">
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>9.654894168104672e-09</v>
+        <v>71.58877551020397</v>
       </c>
       <c r="M23" t="n">
-        <v>26.5478758052941</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="N23" t="n">
-        <v>973.1839638425946</v>
+        <v>997.1488703386009</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>49.61104523615645</v>
+        <v>5.5</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.615721146208671e-09</v>
+        <v>50</v>
       </c>
       <c r="S23" t="n">
-        <v>3.472773166530951</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.07421812367329006</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>39.68883618892517</v>
+        <v>-0</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.308173066012387e-09</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="W23" t="n">
-        <v>460.4080000016648</v>
+        <v>427.1137026239066</v>
       </c>
       <c r="X23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -31430,49 +31430,49 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>121.8894519995391</v>
+        <v>128.9316326530609</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.300867382389072e-13</v>
+        <v>2.879928950908564</v>
       </c>
       <c r="M24" t="n">
-        <v>6.901337038570413</v>
+        <v>3.610551857491373e-13</v>
       </c>
       <c r="N24" t="n">
-        <v>966.212916328887</v>
+        <v>1000</v>
       </c>
       <c r="O24" t="n">
-        <v>3.673416611222035e-12</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9999999999963266</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50.50000000043012</v>
+        <v>41.2399471356222</v>
       </c>
       <c r="R24" t="n">
-        <v>1.881240152101782e-09</v>
+        <v>4.874323167314287e-15</v>
       </c>
       <c r="S24" t="n">
-        <v>3.535000000030108</v>
+        <v>2.886796299493553</v>
       </c>
       <c r="T24" t="n">
-        <v>0.07554800000064348</v>
+        <v>0.06169496091489081</v>
       </c>
       <c r="U24" t="n">
-        <v>40.4000000003441</v>
+        <v>32.99195770849776</v>
       </c>
       <c r="V24" t="n">
-        <v>2.687485931573974e-09</v>
+        <v>6.963318810448982e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>499.9999999992597</v>
+        <v>459.4458211782344</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -31481,7 +31481,7 @@
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.76247299982424e-11</v>
+        <v>-0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -31540,55 +31540,55 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>118.3716326574811</v>
+        <v>102.5744382770325</v>
       </c>
       <c r="K25" t="n">
         <v>13.8592</v>
       </c>
       <c r="L25" t="n">
-        <v>34.1283673428917</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.63372611439172e-09</v>
+        <v>15.48125048850824</v>
       </c>
       <c r="N25" t="n">
-        <v>1000</v>
+        <v>984.3623732439311</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.751059516655908e-11</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.49999999962716</v>
+        <v>51.7272689053132</v>
       </c>
       <c r="R25" t="n">
-        <v>-5.078264848634716e-10</v>
+        <v>2.924593900388572e-14</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.620908823371924</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.07738399428234854</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>41.38181512425056</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.254664069478167e-10</v>
+        <v>4.177991286269389e-14</v>
       </c>
       <c r="W25" t="n">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.999999999932211</v>
+        <v>-0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.778899663828497e-11</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -31843,7 +31843,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>171.5959987631416</v>
+        <v>177.0959987631416</v>
       </c>
       <c r="J2" t="n">
         <v>84.38387755102042</v>
@@ -31867,19 +31867,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31888,10 +31888,10 @@
         <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -31953,22 +31953,22 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>132.2608798977198</v>
+        <v>147.9434397263086</v>
       </c>
       <c r="J3" t="n">
-        <v>84.38387755102046</v>
+        <v>84.3838775510204</v>
       </c>
       <c r="K3" t="n">
         <v>14.1452</v>
       </c>
       <c r="L3" t="n">
-        <v>67.37700234669934</v>
+        <v>50.91468217528821</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.406874616804998e-14</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>186.7032323232324</v>
+        <v>170.4055353535353</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -31977,34 +31977,34 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.04488000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>28.52</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -32072,10 +32072,10 @@
         <v>14.1452</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="M4" t="n">
-        <v>66.03620000000002</v>
+        <v>49.90148</v>
       </c>
       <c r="N4" t="n">
         <v>120</v>
@@ -32090,7 +32090,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>16.13472</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -32102,7 +32102,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>23.04960000000001</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
@@ -32117,7 +32117,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -32239,7 +32239,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -32283,7 +32283,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>247.065444613107</v>
+        <v>247.0654446131071</v>
       </c>
       <c r="J6" t="n">
         <v>85.42265306122449</v>
@@ -32292,13 +32292,13 @@
         <v>15.2312</v>
       </c>
       <c r="L6" t="n">
-        <v>200.6427915518825</v>
+        <v>200.6427915518826</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>318.6363636363636</v>
+        <v>318.6363636363637</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -32402,7 +32402,7 @@
         <v>15.2312</v>
       </c>
       <c r="L7" t="n">
-        <v>3.588599675556061e-14</v>
+        <v>-2.153159805333637e-14</v>
       </c>
       <c r="M7" t="n">
         <v>44.7272</v>
@@ -32512,7 +32512,7 @@
         <v>19.5284</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>-7.177199351112123e-14</v>
       </c>
       <c r="M8" t="n">
         <v>77.18639999999998</v>
@@ -32625,7 +32625,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>74.73639999999999</v>
+        <v>74.73640000000002</v>
       </c>
       <c r="N9" t="n">
         <v>120</v>
@@ -32842,7 +32842,7 @@
         <v>18.1532</v>
       </c>
       <c r="L11" t="n">
-        <v>3.624848157127335e-15</v>
+        <v>-2.508394924732116e-14</v>
       </c>
       <c r="M11" t="n">
         <v>3.552713678800501e-15</v>
@@ -32952,10 +32952,10 @@
         <v>18.1532</v>
       </c>
       <c r="L12" t="n">
-        <v>132.6160595857565</v>
+        <v>132.6160595857566</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.813749233609997e-14</v>
       </c>
       <c r="N12" t="n">
         <v>251.289898989899</v>
@@ -33270,7 +33270,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>126.245306122449</v>
+        <v>126.2453061224489</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -33282,10 +33282,10 @@
         <v>22.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.785611741273897e-14</v>
+        <v>2.813749233609997e-14</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -33392,10 +33392,10 @@
         <v>21.4324</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.392376674115752e-14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-4.178417611910845e-14</v>
       </c>
       <c r="N16" t="n">
         <v>120</v>
@@ -33449,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -33493,7 +33493,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>715.2775510204082</v>
+        <v>294.9600323998592</v>
       </c>
       <c r="J17" t="n">
         <v>160.2775510204082</v>
@@ -33502,13 +33502,13 @@
         <v>16.628</v>
       </c>
       <c r="L17" t="n">
-        <v>600</v>
+        <v>179.682481379451</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>714</v>
+        <v>297.8856565656565</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -33559,7 +33559,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -33603,22 +33603,22 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>301.4600323998595</v>
+        <v>721.7775510204082</v>
       </c>
       <c r="J18" t="n">
-        <v>160.2775510204083</v>
+        <v>160.2775510204082</v>
       </c>
       <c r="K18" t="n">
         <v>16.628</v>
       </c>
       <c r="L18" t="n">
-        <v>179.6824813794512</v>
+        <v>600</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.813749233609997e-14</v>
+        <v>1.125499693443999e-13</v>
       </c>
       <c r="N18" t="n">
-        <v>891.8856565656567</v>
+        <v>891.8856565656564</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -33669,7 +33669,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -33716,19 +33716,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>42.5</v>
+        <v>42.50000000000014</v>
       </c>
       <c r="K19" t="n">
         <v>19.5068</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-4.306319610667274e-14</v>
       </c>
       <c r="M19" t="n">
-        <v>100.6598</v>
+        <v>100.6597999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>790.2090909090911</v>
+        <v>790.2090909090908</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -33838,7 +33838,7 @@
         <v>85.39139999999996</v>
       </c>
       <c r="N20" t="n">
-        <v>703.9551515151518</v>
+        <v>703.9551515151516</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -33948,7 +33948,7 @@
         <v>100.5814000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>602.357777777778</v>
+        <v>602.3577777777778</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -34046,19 +34046,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>13.49999999999996</v>
+        <v>13.50000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>17.85</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.87087974044485e-14</v>
+        <v>2.87087974044485e-14</v>
       </c>
       <c r="M22" t="n">
         <v>124.504</v>
       </c>
       <c r="N22" t="n">
-        <v>476.5961616161617</v>
+        <v>476.5961616161616</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -34162,7 +34162,7 @@
         <v>16.31</v>
       </c>
       <c r="L23" t="n">
-        <v>-7.177199351112123e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="M23" t="n">
         <v>119.9829999999999</v>
@@ -34266,19 +34266,19 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>4.999999999999948</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="K24" t="n">
         <v>16.31</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-2.870879740444849e-14</v>
       </c>
       <c r="M24" t="n">
-        <v>121.4530000000001</v>
+        <v>121.453</v>
       </c>
       <c r="N24" t="n">
-        <v>232.7214141414142</v>
+        <v>232.7214141414141</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
